--- a/dermer_diary.xlsx
+++ b/dermer_diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gil1f\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA2ECEA1-3FB3-4F9D-9338-16051F4E5409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236BC218-669B-430C-9215-51CBCE8BB274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="20098" windowHeight="10671" xr2:uid="{12E3CD63-F060-4377-A472-A4D2DE6149BB}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">גיליון1!$A$1:$F$2101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">גיליון1!$A$1:$F$2098</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3645" uniqueCount="1616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3627" uniqueCount="1616">
   <si>
     <t>נושא</t>
   </si>
@@ -5269,7 +5269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B01A04-1BD8-4DB2-90D3-99A43FE07077}">
-  <dimension ref="A1:G2101"/>
+  <dimension ref="A1:G2098"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.83203125" customWidth="1"/>
@@ -45498,7 +45498,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="2097" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2097" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2097" t="s">
         <v>87</v>
       </c>
@@ -45515,7 +45515,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2098" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2098" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2098" t="s">
         <v>1615</v>
       </c>
@@ -45532,68 +45532,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2099" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F2099" s="3" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="2100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F2100" s="3" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="2101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F2101" s="3" t="s">
-        <v>1231</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F2101" xr:uid="{93B01A04-1BD8-4DB2-90D3-99A43FE07077}"/>
+  <autoFilter ref="A1:F2098" xr:uid="{93B01A04-1BD8-4DB2-90D3-99A43FE07077}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>